--- a/r5-TC-FHIR-AG-Scheduling-R5-129-80---adapt-description-for-central-scheduling-platform/all-profiles.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-129-80---adapt-description-for-central-scheduling-platform/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:31:52+00:00</t>
+    <t>2026-01-28T07:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
